--- a/produtos/Relatorio_Analitico_Mestre.xlsx
+++ b/produtos/Relatorio_Analitico_Mestre.xlsx
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
         <v>1.414</v>
       </c>
       <c r="E2" t="n">
-        <v>36.415</v>
+        <v>35.314</v>
       </c>
       <c r="F2" t="n">
         <v>114.48</v>
       </c>
       <c r="G2" t="n">
-        <v>29.461</v>
+        <v>29.226</v>
       </c>
       <c r="H2" t="n">
-        <v>88.77500000000001</v>
+        <v>88.705</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="3">
@@ -561,22 +561,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
         <v>1.414</v>
       </c>
       <c r="E3" t="n">
-        <v>28.541</v>
+        <v>28.034</v>
       </c>
       <c r="F3" t="n">
         <v>92.2</v>
       </c>
       <c r="G3" t="n">
-        <v>25.051</v>
+        <v>24.797</v>
       </c>
       <c r="H3" t="n">
-        <v>70.575</v>
+        <v>68.56100000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -614,22 +614,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
         <v>1.414</v>
       </c>
       <c r="E4" t="n">
-        <v>107.321</v>
+        <v>102.726</v>
       </c>
       <c r="F4" t="n">
         <v>631.2</v>
       </c>
       <c r="G4" t="n">
-        <v>127.996</v>
+        <v>126.312</v>
       </c>
       <c r="H4" t="n">
-        <v>359.554</v>
+        <v>354.718</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.8307</v>
+        <v>0.4014</v>
       </c>
     </row>
     <row r="5">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="n">
         <v>1.414</v>
       </c>
       <c r="E5" t="n">
-        <v>37.837</v>
+        <v>38.457</v>
       </c>
       <c r="F5" t="n">
         <v>107.8</v>
       </c>
       <c r="G5" t="n">
-        <v>25.589</v>
+        <v>25.607</v>
       </c>
       <c r="H5" t="n">
-        <v>76.22799999999999</v>
+        <v>76.027</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="6">
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
         <v>6.41</v>
       </c>
       <c r="E6" t="n">
-        <v>7.252</v>
+        <v>7.257</v>
       </c>
       <c r="F6" t="n">
         <v>8.44</v>
       </c>
       <c r="G6" t="n">
-        <v>0.409</v>
+        <v>0.398</v>
       </c>
       <c r="H6" t="n">
-        <v>7.845</v>
+        <v>7.827</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6332</v>
+        <v>0.7818000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -773,19 +773,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D7" t="n">
         <v>6.54</v>
       </c>
       <c r="E7" t="n">
-        <v>7.671</v>
+        <v>7.642</v>
       </c>
       <c r="F7" t="n">
         <v>8.91</v>
       </c>
       <c r="G7" t="n">
-        <v>0.475</v>
+        <v>0.478</v>
       </c>
       <c r="H7" t="n">
         <v>8.532</v>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.2469</v>
+        <v>0.07829999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -826,22 +826,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" t="n">
         <v>4.74</v>
       </c>
       <c r="E8" t="n">
-        <v>6.827</v>
+        <v>6.89</v>
       </c>
       <c r="F8" t="n">
-        <v>7.87</v>
+        <v>8.24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.724</v>
       </c>
       <c r="H8" t="n">
-        <v>7.826</v>
+        <v>7.874</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.0296</v>
+        <v>0.0039</v>
       </c>
     </row>
     <row r="9">
@@ -879,22 +879,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="n">
         <v>6.26</v>
       </c>
       <c r="E9" t="n">
-        <v>7.646</v>
+        <v>7.648</v>
       </c>
       <c r="F9" t="n">
         <v>8.66</v>
       </c>
       <c r="G9" t="n">
-        <v>0.473</v>
+        <v>0.468</v>
       </c>
       <c r="H9" t="n">
-        <v>8.379</v>
+        <v>8.378</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.9654</v>
+        <v>0.9166</v>
       </c>
     </row>
     <row r="10">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D10" t="n">
         <v>26.9</v>
       </c>
       <c r="E10" t="n">
-        <v>30.961</v>
+        <v>30.855</v>
       </c>
       <c r="F10" t="n">
         <v>34.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.606</v>
+        <v>1.672</v>
       </c>
       <c r="H10" t="n">
-        <v>33.1</v>
+        <v>33.02</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.0038</v>
+        <v>0.0304</v>
       </c>
     </row>
     <row r="11">
@@ -985,22 +985,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D11" t="n">
         <v>26.9</v>
       </c>
       <c r="E11" t="n">
-        <v>30.27</v>
+        <v>30.216</v>
       </c>
       <c r="F11" t="n">
         <v>33.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.76</v>
+        <v>1.756</v>
       </c>
       <c r="H11" t="n">
-        <v>33.025</v>
+        <v>32.935</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0403</v>
       </c>
     </row>
     <row r="12">
@@ -1038,22 +1038,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
-        <v>27.6</v>
+        <v>26.8</v>
       </c>
       <c r="E12" t="n">
-        <v>31.287</v>
+        <v>31.132</v>
       </c>
       <c r="F12" t="n">
         <v>36.4</v>
       </c>
       <c r="G12" t="n">
-        <v>1.832</v>
+        <v>1.936</v>
       </c>
       <c r="H12" t="n">
-        <v>33.61</v>
+        <v>33.47</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Estável</t>
+          <t>Decrescente (Melhora)</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.0939</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="13">
@@ -1091,22 +1091,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
         <v>26.7</v>
       </c>
       <c r="E13" t="n">
-        <v>31.037</v>
+        <v>31.015</v>
       </c>
       <c r="F13" t="n">
         <v>35.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.235</v>
+        <v>2.212</v>
       </c>
       <c r="H13" t="n">
-        <v>34.4</v>
+        <v>34.385</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.9373</v>
+        <v>0.9481000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>0.707</v>
       </c>
       <c r="E17" t="n">
-        <v>17.528</v>
+        <v>17.162</v>
       </c>
       <c r="F17" t="n">
         <v>159.4</v>
       </c>
       <c r="G17" t="n">
-        <v>30.193</v>
+        <v>29.479</v>
       </c>
       <c r="H17" t="n">
-        <v>64</v>
+        <v>61.8</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.0604</v>
+        <v>0.0594</v>
       </c>
     </row>
     <row r="18">
@@ -1356,22 +1356,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>0.707</v>
       </c>
       <c r="E18" t="n">
-        <v>9.73</v>
+        <v>9.438000000000001</v>
       </c>
       <c r="F18" t="n">
         <v>85.2</v>
       </c>
       <c r="G18" t="n">
-        <v>15.348</v>
+        <v>14.93</v>
       </c>
       <c r="H18" t="n">
-        <v>22.885</v>
+        <v>22.615</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.2994</v>
+        <v>0.2551</v>
       </c>
     </row>
     <row r="19">
@@ -1409,22 +1409,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D19" t="n">
         <v>0.707</v>
       </c>
       <c r="E19" t="n">
-        <v>20.092</v>
+        <v>19.573</v>
       </c>
       <c r="F19" t="n">
         <v>73.8</v>
       </c>
       <c r="G19" t="n">
-        <v>17.578</v>
+        <v>17.394</v>
       </c>
       <c r="H19" t="n">
-        <v>51.3</v>
+        <v>50.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.5545</v>
+        <v>0.3821</v>
       </c>
     </row>
     <row r="20">
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D20" t="n">
         <v>2.25</v>
       </c>
       <c r="E20" t="n">
-        <v>20.405</v>
+        <v>20.354</v>
       </c>
       <c r="F20" t="n">
         <v>179</v>
       </c>
       <c r="G20" t="n">
-        <v>34.814</v>
+        <v>34.398</v>
       </c>
       <c r="H20" t="n">
-        <v>87.565</v>
+        <v>87.14100000000001</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.1244</v>
+        <v>0.2107</v>
       </c>
     </row>
     <row r="21">
@@ -1515,13 +1515,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D21" t="n">
         <v>0.001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="F21" t="n">
         <v>0.007</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.019</v>
+        <v>0.0033</v>
       </c>
     </row>
     <row r="22">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D22" t="n">
         <v>0.001</v>
@@ -1580,7 +1580,7 @@
         <v>0.11</v>
       </c>
       <c r="G22" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="H22" t="n">
         <v>0.007</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.0298</v>
+        <v>0.0066</v>
       </c>
     </row>
     <row r="23">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D23" t="n">
         <v>0.001</v>
@@ -1633,7 +1633,7 @@
         <v>0.03</v>
       </c>
       <c r="G23" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="H23" t="n">
         <v>0.007</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.0016</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="24">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" t="n">
         <v>0.001</v>
@@ -1686,7 +1686,7 @@
         <v>0.007</v>
       </c>
       <c r="G24" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H24" t="n">
         <v>0.007</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.0092</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="25">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D25" t="n">
         <v>0.001</v>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.0141</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="26">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D26" t="n">
         <v>0.001</v>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.0905</v>
+        <v>0.0653</v>
       </c>
     </row>
     <row r="27">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D27" t="n">
         <v>0.001</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.0038</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="28">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D28" t="n">
         <v>0.001</v>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.0735</v>
+        <v>0.0558</v>
       </c>
     </row>
     <row r="29">
@@ -1939,23 +1939,23 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D29" t="n">
         <v>0.004</v>
       </c>
       <c r="E29" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="F29" t="n">
         <v>0.12</v>
       </c>
       <c r="G29" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="H29" t="n">
         <v>0.024</v>
       </c>
-      <c r="H29" t="n">
-        <v>0.025</v>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>0.5</t>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.126</v>
+        <v>0.0653</v>
       </c>
     </row>
     <row r="30">
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D30" t="n">
         <v>0.004</v>
       </c>
       <c r="E30" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="F30" t="n">
         <v>0.017</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.4338</v>
+        <v>0.2596</v>
       </c>
     </row>
     <row r="31">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D31" t="n">
         <v>0.004</v>
@@ -2060,7 +2060,7 @@
         <v>0.008</v>
       </c>
       <c r="H31" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2079,11 +2079,11 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Estável</t>
+          <t>Decrescente (Melhora)</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.0673</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="32">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D32" t="n">
         <v>0.004</v>
@@ -2132,11 +2132,11 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Estável</t>
+          <t>Decrescente (Melhora)</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.0722</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="33">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D33" t="n">
         <v>0.002</v>
@@ -2166,7 +2166,7 @@
         <v>0.011</v>
       </c>
       <c r="H33" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.0078</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="34">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D34" t="n">
         <v>0.002</v>
@@ -2219,7 +2219,7 @@
         <v>0.016</v>
       </c>
       <c r="H34" t="n">
-        <v>0.054</v>
+        <v>0.05</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2238,11 +2238,11 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Estável</t>
+          <t>Decrescente (Melhora)</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.0638</v>
+        <v>0.0228</v>
       </c>
     </row>
     <row r="35">
@@ -2257,22 +2257,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D35" t="n">
         <v>0.002</v>
       </c>
       <c r="E35" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="F35" t="n">
         <v>0.062</v>
       </c>
       <c r="G35" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="H35" t="n">
-        <v>0.055</v>
+        <v>0.054</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Decrescente (Melhora)</t>
+          <t>Estável</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.0399</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="36">
@@ -2310,13 +2310,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D36" t="n">
         <v>0.002</v>
       </c>
       <c r="E36" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F36" t="n">
         <v>0.037</v>
@@ -2325,7 +2325,7 @@
         <v>0.01</v>
       </c>
       <c r="H36" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2344,11 +2344,11 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Decrescente (Melhora)</t>
+          <t>Estável</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.0238</v>
+        <v>0.1101</v>
       </c>
     </row>
     <row r="37">
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D37" t="n">
         <v>0.014</v>
@@ -2375,10 +2375,10 @@
         <v>0.056</v>
       </c>
       <c r="G37" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="H37" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.1587</v>
+        <v>0.3198</v>
       </c>
     </row>
     <row r="38">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D38" t="n">
         <v>0.014</v>
@@ -2450,11 +2450,11 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Crescente (Piora)</t>
+          <t>Estável</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.0499</v>
+        <v>0.1095</v>
       </c>
     </row>
     <row r="39">
@@ -2469,22 +2469,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D39" t="n">
         <v>0.014</v>
       </c>
       <c r="E39" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="F39" t="n">
         <v>0.132</v>
       </c>
       <c r="G39" t="n">
-        <v>0.027</v>
+        <v>0.026</v>
       </c>
       <c r="H39" t="n">
-        <v>0.057</v>
+        <v>0.053</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.9203</v>
+        <v>0.9275</v>
       </c>
     </row>
     <row r="40">
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D40" t="n">
         <v>0.014</v>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.2475</v>
+        <v>0.3153</v>
       </c>
     </row>
     <row r="41">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D41" t="n">
         <v>0.014</v>
@@ -2590,7 +2590,7 @@
         <v>0.011</v>
       </c>
       <c r="H41" t="n">
-        <v>0.044</v>
+        <v>0.043</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.5244</v>
+        <v>0.4045</v>
       </c>
     </row>
     <row r="42">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D42" t="n">
         <v>0.014</v>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.5977</v>
+        <v>0.5326</v>
       </c>
     </row>
     <row r="43">
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D43" t="n">
         <v>0.014</v>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D44" t="n">
         <v>0.014</v>
@@ -2787,22 +2787,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.193</v>
+        <v>0.21</v>
       </c>
       <c r="F45" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="G45" t="n">
-        <v>0.155</v>
+        <v>0.17</v>
       </c>
       <c r="H45" t="n">
-        <v>0.533</v>
+        <v>0.556</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2840,22 +2840,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D46" t="n">
         <v>0.04</v>
       </c>
       <c r="E46" t="n">
-        <v>0.375</v>
+        <v>0.379</v>
       </c>
       <c r="F46" t="n">
         <v>1.12</v>
       </c>
       <c r="G46" t="n">
-        <v>0.305</v>
+        <v>0.311</v>
       </c>
       <c r="H46" t="n">
-        <v>1.038</v>
+        <v>1.026</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.0213</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="47">
@@ -2893,22 +2893,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D47" t="n">
         <v>0.057</v>
       </c>
       <c r="E47" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.522</v>
       </c>
       <c r="F47" t="n">
         <v>3.22</v>
       </c>
       <c r="G47" t="n">
-        <v>0.71</v>
+        <v>0.694</v>
       </c>
       <c r="H47" t="n">
-        <v>1.643</v>
+        <v>1.596</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.0302</v>
+        <v>0.0037</v>
       </c>
     </row>
     <row r="48">
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D48" t="n">
         <v>0.01</v>
       </c>
       <c r="E48" t="n">
-        <v>0.192</v>
+        <v>0.21</v>
       </c>
       <c r="F48" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="G48" t="n">
-        <v>0.179</v>
+        <v>0.198</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.617</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2999,22 +2999,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D49" t="n">
         <v>0.01</v>
       </c>
       <c r="E49" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="F49" t="n">
         <v>0.21</v>
       </c>
       <c r="G49" t="n">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="H49" t="n">
-        <v>0.184</v>
+        <v>0.183</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.6531</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="50">
@@ -3052,22 +3052,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D50" t="n">
         <v>0.01</v>
       </c>
       <c r="E50" t="n">
-        <v>0.111</v>
+        <v>0.108</v>
       </c>
       <c r="F50" t="n">
         <v>0.6</v>
       </c>
       <c r="G50" t="n">
-        <v>0.123</v>
+        <v>0.121</v>
       </c>
       <c r="H50" t="n">
-        <v>0.334</v>
+        <v>0.32</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.0179</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -3105,22 +3105,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D51" t="n">
         <v>0.046</v>
       </c>
       <c r="E51" t="n">
-        <v>0.114</v>
+        <v>0.109</v>
       </c>
       <c r="F51" t="n">
         <v>0.75</v>
       </c>
       <c r="G51" t="n">
-        <v>0.161</v>
+        <v>0.156</v>
       </c>
       <c r="H51" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.2072</v>
+        <v>0.1057</v>
       </c>
     </row>
     <row r="52">
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D52" t="n">
         <v>0.03</v>
       </c>
       <c r="E52" t="n">
-        <v>0.113</v>
+        <v>0.115</v>
       </c>
       <c r="F52" t="n">
         <v>0.4</v>
       </c>
       <c r="G52" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="H52" t="n">
-        <v>0.31</v>
+        <v>0.309</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1916</v>
       </c>
     </row>
     <row r="53">
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0.9273</v>
       </c>
     </row>
     <row r="57">
@@ -3423,22 +3423,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D57" t="n">
         <v>0.008</v>
       </c>
       <c r="E57" t="n">
-        <v>0.257</v>
+        <v>0.247</v>
       </c>
       <c r="F57" t="n">
         <v>2.18</v>
       </c>
       <c r="G57" t="n">
-        <v>0.43</v>
+        <v>0.421</v>
       </c>
       <c r="H57" t="n">
-        <v>0.965</v>
+        <v>0.962</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.619</v>
+        <v>0.8547</v>
       </c>
     </row>
     <row r="58">
@@ -3476,22 +3476,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D58" t="n">
         <v>0.001</v>
       </c>
       <c r="E58" t="n">
-        <v>0.106</v>
+        <v>0.101</v>
       </c>
       <c r="F58" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>0.186</v>
+        <v>0.182</v>
       </c>
       <c r="H58" t="n">
-        <v>0.405</v>
+        <v>0.386</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.2525</v>
+        <v>0.5217000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -3529,22 +3529,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D59" t="n">
         <v>0.014</v>
       </c>
       <c r="E59" t="n">
-        <v>1.508</v>
+        <v>1.382</v>
       </c>
       <c r="F59" t="n">
         <v>13.24</v>
       </c>
       <c r="G59" t="n">
-        <v>3.455</v>
+        <v>3.321</v>
       </c>
       <c r="H59" t="n">
-        <v>8.59</v>
+        <v>8.308999999999999</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.023</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="60">
@@ -3582,22 +3582,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D60" t="n">
         <v>0.014</v>
       </c>
       <c r="E60" t="n">
-        <v>0.438</v>
+        <v>0.424</v>
       </c>
       <c r="F60" t="n">
         <v>5.92</v>
       </c>
       <c r="G60" t="n">
-        <v>1.11</v>
+        <v>1.094</v>
       </c>
       <c r="H60" t="n">
-        <v>1.454</v>
+        <v>1.42</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.3257</v>
+        <v>0.1675</v>
       </c>
     </row>
     <row r="61">
@@ -3635,22 +3635,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D61" t="n">
         <v>0.001</v>
       </c>
       <c r="E61" t="n">
-        <v>0.023</v>
+        <v>0.021</v>
       </c>
       <c r="F61" t="n">
         <v>0.424</v>
       </c>
       <c r="G61" t="n">
-        <v>0.089</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>0.075</v>
+        <v>0.066</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>0.0003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3688,22 +3688,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D62" t="n">
         <v>0.001</v>
       </c>
       <c r="E62" t="n">
-        <v>0.145</v>
+        <v>0.133</v>
       </c>
       <c r="F62" t="n">
         <v>2.88</v>
       </c>
       <c r="G62" t="n">
-        <v>0.603</v>
+        <v>0.578</v>
       </c>
       <c r="H62" t="n">
-        <v>0.382</v>
+        <v>0.34</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0.0002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D63" t="n">
         <v>0.001</v>
@@ -3753,7 +3753,7 @@
         <v>0.082</v>
       </c>
       <c r="G63" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="H63" t="n">
         <v>0.007</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.001</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="64">
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D64" t="n">
         <v>0.001</v>
@@ -3809,7 +3809,7 @@
         <v>0.011</v>
       </c>
       <c r="H64" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>0.5580000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -3847,22 +3847,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D65" t="n">
         <v>0.001</v>
       </c>
       <c r="E65" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="F65" t="n">
         <v>0.192</v>
       </c>
       <c r="G65" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="H65" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>0.7809</v>
+        <v>0.9766</v>
       </c>
     </row>
     <row r="66">
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D66" t="n">
         <v>0.001</v>
@@ -3912,10 +3912,10 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="H66" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>0.0148</v>
+        <v>0.0051</v>
       </c>
     </row>
     <row r="67">
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D67" t="n">
         <v>0.001</v>
       </c>
       <c r="E67" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="F67" t="n">
         <v>0.424</v>
       </c>
       <c r="G67" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4006,22 +4006,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D68" t="n">
         <v>0.001</v>
       </c>
       <c r="E68" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="F68" t="n">
         <v>0.424</v>
       </c>
       <c r="G68" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D69" t="n">
         <v>0.001</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>0.0011</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="70">
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D70" t="n">
         <v>0.001</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>0.0092</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="71">
@@ -4165,22 +4165,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D71" t="n">
         <v>0.001</v>
       </c>
       <c r="E71" t="n">
-        <v>0.102</v>
+        <v>0.099</v>
       </c>
       <c r="F71" t="n">
         <v>0.48</v>
       </c>
       <c r="G71" t="n">
-        <v>0.108</v>
+        <v>0.104</v>
       </c>
       <c r="H71" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="72">
@@ -4218,19 +4218,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D72" t="n">
         <v>0.02</v>
       </c>
       <c r="E72" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
       <c r="F72" t="n">
         <v>0.34</v>
       </c>
       <c r="G72" t="n">
-        <v>0.066</v>
+        <v>0.063</v>
       </c>
       <c r="H72" t="n">
         <v>0.2</v>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>0.0044</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="73">
@@ -4271,19 +4271,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D73" t="n">
         <v>0.07099999999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>0.202</v>
+        <v>0.198</v>
       </c>
       <c r="F73" t="n">
         <v>0.51</v>
       </c>
       <c r="G73" t="n">
-        <v>0.161</v>
+        <v>0.156</v>
       </c>
       <c r="H73" t="n">
         <v>0.47</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>0.4546</v>
+        <v>0.4609</v>
       </c>
     </row>
     <row r="74">
@@ -4324,22 +4324,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D74" t="n">
         <v>0.001</v>
       </c>
       <c r="E74" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="F74" t="n">
         <v>0.6</v>
       </c>
       <c r="G74" t="n">
-        <v>0.124</v>
+        <v>0.121</v>
       </c>
       <c r="H74" t="n">
-        <v>0.124</v>
+        <v>0.097</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>0.2214</v>
+        <v>0.2259</v>
       </c>
     </row>
     <row r="75">
@@ -4377,19 +4377,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="F75" t="n">
         <v>0.424</v>
       </c>
       <c r="G75" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H75" t="n">
         <v>0.001</v>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>0.0268</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="76">
@@ -4430,19 +4430,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="F76" t="n">
         <v>0.424</v>
       </c>
       <c r="G76" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H76" t="n">
         <v>0.001</v>
@@ -4468,7 +4468,7 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>0.0268</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="77">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D77" t="n">
         <v>0.001</v>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>0.0036</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="78">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D78" t="n">
         <v>0.001</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>0.0092</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="79">
@@ -4589,19 +4589,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="F79" t="n">
         <v>0.424</v>
       </c>
       <c r="G79" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H79" t="n">
         <v>0.001</v>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>0.0103</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="80">
@@ -4642,19 +4642,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="F80" t="n">
         <v>0.424</v>
       </c>
       <c r="G80" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H80" t="n">
         <v>0.001</v>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>0.0103</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="81">
@@ -4695,22 +4695,22 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D81" t="n">
         <v>0.001</v>
       </c>
       <c r="E81" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="F81" t="n">
         <v>0.424</v>
       </c>
       <c r="G81" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>0.0004</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="82">
@@ -4748,22 +4748,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D82" t="n">
         <v>0.001</v>
       </c>
       <c r="E82" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="F82" t="n">
         <v>0.424</v>
       </c>
       <c r="G82" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -4801,22 +4801,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D83" t="n">
         <v>0.001</v>
       </c>
       <c r="E83" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="F83" t="n">
         <v>0.211</v>
       </c>
       <c r="G83" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="H83" t="n">
-        <v>0.149</v>
+        <v>0.148</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>0.0053</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D84" t="n">
         <v>0.001</v>
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>0.0092</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="85">
@@ -4907,19 +4907,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D85" t="n">
         <v>0.001</v>
       </c>
       <c r="E85" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="F85" t="n">
         <v>0.424</v>
       </c>
       <c r="G85" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H85" t="n">
         <v>0.002</v>
@@ -4941,11 +4941,11 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Estável</t>
+          <t>Crescente (Piora)</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>0.1545</v>
+        <v>0.0409</v>
       </c>
     </row>
     <row r="86">
@@ -4960,19 +4960,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D86" t="n">
         <v>0.001</v>
       </c>
       <c r="E86" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="F86" t="n">
         <v>0.424</v>
       </c>
       <c r="G86" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H86" t="n">
         <v>0.002</v>
@@ -4994,11 +4994,11 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Estável</t>
+          <t>Crescente (Piora)</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>0.1545</v>
+        <v>0.0409</v>
       </c>
     </row>
     <row r="87">
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D87" t="n">
         <v>0.001</v>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>0.0011</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="88">
@@ -5066,7 +5066,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D88" t="n">
         <v>0.001</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>0.0092</v>
+        <v>0.0032</v>
       </c>
     </row>
   </sheetData>
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23.271</v>
+        <v>21.497</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47.706</v>
+        <v>41.405</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -5206,10 +5206,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.293</v>
+        <v>5.934</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0982</v>
+        <v>0.1149</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12.522</v>
+        <v>11.765</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0058</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.552</v>
+        <v>1.674</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6704</v>
+        <v>0.6428</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.534</v>
+        <v>2.519</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4692</v>
+        <v>0.4719</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.762</v>
+        <v>0.924</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8586</v>
+        <v>0.8196</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -5344,10 +5344,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.032</v>
+        <v>1.096</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7936</v>
+        <v>0.7781</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.942</v>
+        <v>1.832</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5845</v>
+        <v>0.608</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.567</v>
+        <v>5.5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1347</v>
+        <v>0.1386</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.467</v>
+        <v>11.317</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0009</v>
+        <v>0.0101</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.829000000000001</v>
+        <v>10.26</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0316</v>
+        <v>0.0165</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.722</v>
+        <v>3.842</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2931</v>
+        <v>0.279</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.769</v>
+        <v>10.779</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0206</v>
+        <v>0.013</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.442</v>
+        <v>4.297</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2175</v>
+        <v>0.2311</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.249</v>
+        <v>0.418</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6176</v>
+        <v>0.5182</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.845</v>
+        <v>0.714</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8386</v>
+        <v>0.8699</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20.448</v>
+        <v>22.637</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.04</v>
+        <v>0.164</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9979</v>
+        <v>0.9832</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.541</v>
+        <v>1.7</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4679</v>
+        <v>0.6368</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.503</v>
+        <v>1.62</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6816</v>
+        <v>0.655</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>

--- a/produtos/Relatorio_Analitico_Mestre.xlsx
+++ b/produtos/Relatorio_Analitico_Mestre.xlsx
@@ -508,22 +508,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D2" t="n">
         <v>1.414</v>
       </c>
       <c r="E2" t="n">
-        <v>35.314</v>
+        <v>34.445</v>
       </c>
       <c r="F2" t="n">
         <v>114.48</v>
       </c>
       <c r="G2" t="n">
-        <v>29.226</v>
+        <v>29.345</v>
       </c>
       <c r="H2" t="n">
-        <v>88.705</v>
+        <v>88.67</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>0.0003</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="3">
@@ -561,22 +561,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D3" t="n">
         <v>1.414</v>
       </c>
       <c r="E3" t="n">
-        <v>28.034</v>
+        <v>27.351</v>
       </c>
       <c r="F3" t="n">
         <v>92.2</v>
       </c>
       <c r="G3" t="n">
-        <v>24.797</v>
+        <v>24.838</v>
       </c>
       <c r="H3" t="n">
-        <v>68.56100000000001</v>
+        <v>67.554</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -614,22 +614,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
         <v>1.414</v>
       </c>
       <c r="E4" t="n">
-        <v>102.726</v>
+        <v>101.051</v>
       </c>
       <c r="F4" t="n">
         <v>631.2</v>
       </c>
       <c r="G4" t="n">
-        <v>126.312</v>
+        <v>125.184</v>
       </c>
       <c r="H4" t="n">
-        <v>354.718</v>
+        <v>352.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.4014</v>
+        <v>0.3229</v>
       </c>
     </row>
     <row r="5">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
         <v>1.414</v>
       </c>
       <c r="E5" t="n">
-        <v>38.457</v>
+        <v>38.03</v>
       </c>
       <c r="F5" t="n">
         <v>107.8</v>
       </c>
       <c r="G5" t="n">
-        <v>25.607</v>
+        <v>25.465</v>
       </c>
       <c r="H5" t="n">
-        <v>76.027</v>
+        <v>75.82599999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
         <v>6.41</v>
       </c>
       <c r="E6" t="n">
-        <v>7.257</v>
+        <v>7.251</v>
       </c>
       <c r="F6" t="n">
         <v>8.44</v>
       </c>
       <c r="G6" t="n">
-        <v>0.398</v>
+        <v>0.395</v>
       </c>
       <c r="H6" t="n">
-        <v>7.827</v>
+        <v>7.818</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.5857</v>
       </c>
     </row>
     <row r="7">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" t="n">
         <v>6.54</v>
       </c>
       <c r="E7" t="n">
-        <v>7.642</v>
+        <v>7.622</v>
       </c>
       <c r="F7" t="n">
         <v>8.91</v>
       </c>
       <c r="G7" t="n">
-        <v>0.478</v>
+        <v>0.489</v>
       </c>
       <c r="H7" t="n">
-        <v>8.532</v>
+        <v>8.531000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -807,11 +807,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Estável</t>
+          <t>Decrescente (Melhora)</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0332</v>
       </c>
     </row>
     <row r="8">
@@ -826,22 +826,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
         <v>4.74</v>
       </c>
       <c r="E8" t="n">
-        <v>6.89</v>
+        <v>6.861</v>
       </c>
       <c r="F8" t="n">
         <v>8.24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.724</v>
+        <v>0.739</v>
       </c>
       <c r="H8" t="n">
-        <v>7.874</v>
+        <v>7.87</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.0039</v>
+        <v>0.0183</v>
       </c>
     </row>
     <row r="9">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="n">
         <v>6.26</v>
@@ -891,10 +891,10 @@
         <v>8.66</v>
       </c>
       <c r="G9" t="n">
-        <v>0.468</v>
+        <v>0.462</v>
       </c>
       <c r="H9" t="n">
-        <v>8.378</v>
+        <v>8.377000000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.9166</v>
+        <v>0.9919</v>
       </c>
     </row>
     <row r="10">
@@ -932,22 +932,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" t="n">
         <v>26.9</v>
       </c>
       <c r="E10" t="n">
-        <v>30.855</v>
+        <v>30.805</v>
       </c>
       <c r="F10" t="n">
         <v>34.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.672</v>
+        <v>1.679</v>
       </c>
       <c r="H10" t="n">
-        <v>33.02</v>
+        <v>32.98</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -966,11 +966,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Crescente (Piora)</t>
+          <t>Estável</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.0304</v>
+        <v>0.09470000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -985,22 +985,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" t="n">
         <v>26.9</v>
       </c>
       <c r="E11" t="n">
-        <v>30.216</v>
+        <v>30.172</v>
       </c>
       <c r="F11" t="n">
         <v>33.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.756</v>
+        <v>1.754</v>
       </c>
       <c r="H11" t="n">
-        <v>32.935</v>
+        <v>32.89</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1019,11 +1019,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Crescente (Piora)</t>
+          <t>Estável</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.0403</v>
+        <v>0.0878</v>
       </c>
     </row>
     <row r="12">
@@ -1038,22 +1038,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="n">
         <v>26.8</v>
       </c>
       <c r="E12" t="n">
-        <v>31.132</v>
+        <v>31.092</v>
       </c>
       <c r="F12" t="n">
         <v>36.4</v>
       </c>
       <c r="G12" t="n">
-        <v>1.936</v>
+        <v>1.929</v>
       </c>
       <c r="H12" t="n">
-        <v>33.47</v>
+        <v>33.4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.0251</v>
+        <v>0.0161</v>
       </c>
     </row>
     <row r="13">
@@ -1091,22 +1091,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>26.7</v>
       </c>
       <c r="E13" t="n">
-        <v>31.015</v>
+        <v>30.917</v>
       </c>
       <c r="F13" t="n">
         <v>35.5</v>
       </c>
       <c r="G13" t="n">
-        <v>2.212</v>
+        <v>2.278</v>
       </c>
       <c r="H13" t="n">
-        <v>34.385</v>
+        <v>34.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.6299</v>
       </c>
     </row>
     <row r="14">
@@ -1303,22 +1303,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>0.707</v>
       </c>
       <c r="E17" t="n">
-        <v>17.162</v>
+        <v>16.729</v>
       </c>
       <c r="F17" t="n">
         <v>159.4</v>
       </c>
       <c r="G17" t="n">
-        <v>29.479</v>
+        <v>29.2</v>
       </c>
       <c r="H17" t="n">
-        <v>61.8</v>
+        <v>60.7</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1337,11 +1337,11 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Estável</t>
+          <t>Decrescente (Melhora)</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.0594</v>
+        <v>0.0241</v>
       </c>
     </row>
     <row r="18">
@@ -1356,22 +1356,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>0.707</v>
       </c>
       <c r="E18" t="n">
-        <v>9.438000000000001</v>
+        <v>9.173</v>
       </c>
       <c r="F18" t="n">
         <v>85.2</v>
       </c>
       <c r="G18" t="n">
-        <v>14.93</v>
+        <v>14.773</v>
       </c>
       <c r="H18" t="n">
-        <v>22.615</v>
+        <v>22.48</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.2551</v>
+        <v>0.1192</v>
       </c>
     </row>
     <row r="19">
@@ -1409,22 +1409,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D19" t="n">
         <v>0.707</v>
       </c>
       <c r="E19" t="n">
-        <v>19.573</v>
+        <v>19.403</v>
       </c>
       <c r="F19" t="n">
         <v>73.8</v>
       </c>
       <c r="G19" t="n">
-        <v>17.394</v>
+        <v>17.21</v>
       </c>
       <c r="H19" t="n">
-        <v>50.3</v>
+        <v>49.8</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>RISCO</t>
+          <t>ROBUSTO</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.3821</v>
+        <v>0.4121</v>
       </c>
     </row>
     <row r="20">
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D20" t="n">
-        <v>2.25</v>
+        <v>0.707</v>
       </c>
       <c r="E20" t="n">
-        <v>20.354</v>
+        <v>19.907</v>
       </c>
       <c r="F20" t="n">
         <v>179</v>
       </c>
       <c r="G20" t="n">
-        <v>34.398</v>
+        <v>34.125</v>
       </c>
       <c r="H20" t="n">
-        <v>87.14100000000001</v>
+        <v>86.717</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.2107</v>
+        <v>0.0997</v>
       </c>
     </row>
     <row r="21">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" t="n">
         <v>0.001</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0.0033</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="22">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D22" t="n">
         <v>0.001</v>
@@ -1580,7 +1580,7 @@
         <v>0.11</v>
       </c>
       <c r="G22" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
       <c r="H22" t="n">
         <v>0.007</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.0066</v>
+        <v>0.0033</v>
       </c>
     </row>
     <row r="23">
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
         <v>0.001</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0.0004</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="24">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D24" t="n">
         <v>0.001</v>
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>0.0032</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="25">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D25" t="n">
         <v>0.001</v>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0.0124</v>
+        <v>0.0117</v>
       </c>
     </row>
     <row r="26">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D26" t="n">
         <v>0.001</v>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0.0653</v>
+        <v>0.0562</v>
       </c>
     </row>
     <row r="27">
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D27" t="n">
         <v>0.001</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0.0025</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="28">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D28" t="n">
         <v>0.001</v>
@@ -1920,11 +1920,11 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Estável</t>
+          <t>Decrescente (Melhora)</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.0558</v>
+        <v>0.0432</v>
       </c>
     </row>
     <row r="29">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D29" t="n">
         <v>0.004</v>
@@ -1973,11 +1973,11 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Estável</t>
+          <t>Decrescente (Melhora)</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.0653</v>
+        <v>0.0479</v>
       </c>
     </row>
     <row r="30">
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D30" t="n">
         <v>0.004</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>0.2596</v>
+        <v>0.2015</v>
       </c>
     </row>
     <row r="31">
@@ -2045,22 +2045,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
         <v>0.004</v>
       </c>
       <c r="E31" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F31" t="n">
         <v>0.033</v>
       </c>
       <c r="G31" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0.022</v>
+        <v>0.027</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2079,11 +2079,11 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Decrescente (Melhora)</t>
+          <t>Estável</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>0.0389</v>
+        <v>0.2256</v>
       </c>
     </row>
     <row r="32">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D32" t="n">
         <v>0.004</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0.0458</v>
+        <v>0.0298</v>
       </c>
     </row>
     <row r="33">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D33" t="n">
         <v>0.002</v>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>0.003</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="34">
@@ -2204,22 +2204,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D34" t="n">
         <v>0.002</v>
       </c>
       <c r="E34" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="F34" t="n">
         <v>0.06</v>
       </c>
       <c r="G34" t="n">
-        <v>0.016</v>
+        <v>0.015</v>
       </c>
       <c r="H34" t="n">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0.0228</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="35">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D35" t="n">
         <v>0.002</v>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0.056</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="36">
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36" t="n">
         <v>0.002</v>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0.1101</v>
+        <v>0.2227</v>
       </c>
     </row>
     <row r="37">
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D37" t="n">
         <v>0.014</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>0.3198</v>
+        <v>0.4163</v>
       </c>
     </row>
     <row r="38">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D38" t="n">
         <v>0.014</v>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0.1095</v>
+        <v>0.1494</v>
       </c>
     </row>
     <row r="39">
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D39" t="n">
         <v>0.014</v>
@@ -2481,10 +2481,10 @@
         <v>0.132</v>
       </c>
       <c r="G39" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="H39" t="n">
-        <v>0.053</v>
+        <v>0.051</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0.9275</v>
+        <v>0.8279</v>
       </c>
     </row>
     <row r="40">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D40" t="n">
         <v>0.014</v>
       </c>
       <c r="E40" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="F40" t="n">
         <v>0.021</v>
@@ -2537,7 +2537,7 @@
         <v>0.002</v>
       </c>
       <c r="H40" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>0.3153</v>
+        <v>0.3859</v>
       </c>
     </row>
     <row r="41">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D41" t="n">
         <v>0.014</v>
@@ -2587,10 +2587,10 @@
         <v>0.056</v>
       </c>
       <c r="G41" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="H41" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.4045</v>
+        <v>0.3574</v>
       </c>
     </row>
     <row r="42">
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D42" t="n">
         <v>0.014</v>
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0.5326</v>
+        <v>0.505</v>
       </c>
     </row>
     <row r="43">
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D43" t="n">
         <v>0.014</v>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D44" t="n">
         <v>0.014</v>
@@ -2787,13 +2787,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0.21</v>
+        <v>0.214</v>
       </c>
       <c r="F45" t="n">
         <v>0.65</v>
@@ -2802,7 +2802,7 @@
         <v>0.17</v>
       </c>
       <c r="H45" t="n">
-        <v>0.556</v>
+        <v>0.552</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2840,22 +2840,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D46" t="n">
         <v>0.04</v>
       </c>
       <c r="E46" t="n">
-        <v>0.379</v>
+        <v>0.386</v>
       </c>
       <c r="F46" t="n">
         <v>1.12</v>
       </c>
       <c r="G46" t="n">
-        <v>0.311</v>
+        <v>0.309</v>
       </c>
       <c r="H46" t="n">
-        <v>1.026</v>
+        <v>1.021</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0.0335</v>
+        <v>0.0201</v>
       </c>
     </row>
     <row r="47">
@@ -2893,22 +2893,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D47" t="n">
         <v>0.057</v>
       </c>
       <c r="E47" t="n">
-        <v>0.522</v>
+        <v>0.511</v>
       </c>
       <c r="F47" t="n">
         <v>3.22</v>
       </c>
       <c r="G47" t="n">
-        <v>0.694</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>1.596</v>
+        <v>1.572</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>0.0037</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="48">
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D48" t="n">
         <v>0.01</v>
       </c>
       <c r="E48" t="n">
-        <v>0.21</v>
+        <v>0.212</v>
       </c>
       <c r="F48" t="n">
         <v>0.66</v>
       </c>
       <c r="G48" t="n">
-        <v>0.198</v>
+        <v>0.194</v>
       </c>
       <c r="H48" t="n">
-        <v>0.617</v>
+        <v>0.615</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D49" t="n">
         <v>0.01</v>
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>0.577</v>
+        <v>0.5442</v>
       </c>
     </row>
     <row r="50">
@@ -3052,22 +3052,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D50" t="n">
         <v>0.01</v>
       </c>
       <c r="E50" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="F50" t="n">
         <v>0.6</v>
       </c>
       <c r="G50" t="n">
-        <v>0.121</v>
+        <v>0.119</v>
       </c>
       <c r="H50" t="n">
-        <v>0.32</v>
+        <v>0.312</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="M50" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0065</v>
       </c>
     </row>
     <row r="51">
@@ -3105,22 +3105,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D51" t="n">
         <v>0.046</v>
       </c>
       <c r="E51" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="F51" t="n">
         <v>0.75</v>
       </c>
       <c r="G51" t="n">
-        <v>0.156</v>
+        <v>0.153</v>
       </c>
       <c r="H51" t="n">
-        <v>0.39</v>
+        <v>0.379</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0.1057</v>
+        <v>0.07630000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D52" t="n">
         <v>0.03</v>
@@ -3170,10 +3170,10 @@
         <v>0.4</v>
       </c>
       <c r="G52" t="n">
-        <v>0.093</v>
+        <v>0.091</v>
       </c>
       <c r="H52" t="n">
-        <v>0.309</v>
+        <v>0.308</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.1916</v>
+        <v>0.3362</v>
       </c>
     </row>
     <row r="53">
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0.9273</v>
+        <v>0.8623</v>
       </c>
     </row>
     <row r="57">
@@ -3423,22 +3423,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D57" t="n">
         <v>0.008</v>
       </c>
       <c r="E57" t="n">
-        <v>0.247</v>
+        <v>0.241</v>
       </c>
       <c r="F57" t="n">
         <v>2.18</v>
       </c>
       <c r="G57" t="n">
-        <v>0.421</v>
+        <v>0.416</v>
       </c>
       <c r="H57" t="n">
-        <v>0.962</v>
+        <v>0.96</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>0.8547</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="58">
@@ -3476,22 +3476,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D58" t="n">
         <v>0.001</v>
       </c>
       <c r="E58" t="n">
-        <v>0.101</v>
+        <v>0.098</v>
       </c>
       <c r="F58" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>0.182</v>
+        <v>0.18</v>
       </c>
       <c r="H58" t="n">
-        <v>0.386</v>
+        <v>0.376</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="M58" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.6748</v>
       </c>
     </row>
     <row r="59">
@@ -3529,22 +3529,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D59" t="n">
         <v>0.014</v>
       </c>
       <c r="E59" t="n">
-        <v>1.382</v>
+        <v>1.325</v>
       </c>
       <c r="F59" t="n">
         <v>13.24</v>
       </c>
       <c r="G59" t="n">
-        <v>3.321</v>
+        <v>3.26</v>
       </c>
       <c r="H59" t="n">
-        <v>8.308999999999999</v>
+        <v>8.167999999999999</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.0108</v>
+        <v>0.0066</v>
       </c>
     </row>
     <row r="60">
@@ -3582,22 +3582,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D60" t="n">
         <v>0.014</v>
       </c>
       <c r="E60" t="n">
-        <v>0.424</v>
+        <v>0.411</v>
       </c>
       <c r="F60" t="n">
         <v>5.92</v>
       </c>
       <c r="G60" t="n">
-        <v>1.094</v>
+        <v>1.078</v>
       </c>
       <c r="H60" t="n">
-        <v>1.42</v>
+        <v>1.387</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0.1675</v>
+        <v>0.0815</v>
       </c>
     </row>
     <row r="61">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D61" t="n">
         <v>0.001</v>
@@ -3647,10 +3647,10 @@
         <v>0.424</v>
       </c>
       <c r="G61" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>0.066</v>
+        <v>0.062</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3688,22 +3688,22 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D62" t="n">
         <v>0.001</v>
       </c>
       <c r="E62" t="n">
-        <v>0.133</v>
+        <v>0.128</v>
       </c>
       <c r="F62" t="n">
         <v>2.88</v>
       </c>
       <c r="G62" t="n">
-        <v>0.578</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>0.34</v>
+        <v>0.319</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D63" t="n">
         <v>0.001</v>
@@ -3753,10 +3753,10 @@
         <v>0.082</v>
       </c>
       <c r="G63" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
       <c r="H63" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="64">
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D64" t="n">
         <v>0.001</v>
@@ -3806,10 +3806,10 @@
         <v>0.04</v>
       </c>
       <c r="G64" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="H64" t="n">
-        <v>0.028</v>
+        <v>0.027</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0.8615</v>
       </c>
     </row>
     <row r="65">
@@ -3847,22 +3847,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D65" t="n">
         <v>0.001</v>
       </c>
       <c r="E65" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="F65" t="n">
         <v>0.192</v>
       </c>
       <c r="G65" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="H65" t="n">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>0.9766</v>
+        <v>0.5498</v>
       </c>
     </row>
     <row r="66">
@@ -3900,13 +3900,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D66" t="n">
         <v>0.001</v>
       </c>
       <c r="E66" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="F66" t="n">
         <v>0.06900000000000001</v>
@@ -3915,7 +3915,7 @@
         <v>0.017</v>
       </c>
       <c r="H66" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>0.0051</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="67">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D67" t="n">
         <v>0.001</v>
@@ -3965,7 +3965,7 @@
         <v>0.424</v>
       </c>
       <c r="G67" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="H67" t="n">
         <v>0.006</v>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D68" t="n">
         <v>0.001</v>
@@ -4018,7 +4018,7 @@
         <v>0.424</v>
       </c>
       <c r="G68" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="H68" t="n">
         <v>0.006</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D69" t="n">
         <v>0.001</v>
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="M69" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="70">
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D70" t="n">
         <v>0.001</v>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>0.0032</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="71">
@@ -4165,22 +4165,22 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D71" t="n">
         <v>0.001</v>
       </c>
       <c r="E71" t="n">
-        <v>0.099</v>
+        <v>0.11</v>
       </c>
       <c r="F71" t="n">
         <v>0.48</v>
       </c>
       <c r="G71" t="n">
-        <v>0.104</v>
+        <v>0.117</v>
       </c>
       <c r="H71" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>0.0023</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="72">
@@ -4218,22 +4218,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D72" t="n">
         <v>0.02</v>
       </c>
       <c r="E72" t="n">
-        <v>0.089</v>
+        <v>0.096</v>
       </c>
       <c r="F72" t="n">
         <v>0.34</v>
       </c>
       <c r="G72" t="n">
-        <v>0.063</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2</v>
+        <v>0.256</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>0.0133</v>
+        <v>0.0036</v>
       </c>
     </row>
     <row r="73">
@@ -4271,19 +4271,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D73" t="n">
         <v>0.07099999999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>0.198</v>
+        <v>0.196</v>
       </c>
       <c r="F73" t="n">
         <v>0.51</v>
       </c>
       <c r="G73" t="n">
-        <v>0.156</v>
+        <v>0.152</v>
       </c>
       <c r="H73" t="n">
         <v>0.47</v>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>0.4609</v>
+        <v>0.5397999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -4324,23 +4324,23 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D74" t="n">
         <v>0.001</v>
       </c>
       <c r="E74" t="n">
-        <v>0.092</v>
+        <v>0.12</v>
       </c>
       <c r="F74" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H74" t="n">
         <v>0.6</v>
       </c>
-      <c r="G74" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.097</v>
-      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>0.5</t>
@@ -4348,12 +4348,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>ROBUSTO</t>
+          <t>RISCO</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="M74" t="n">
-        <v>0.2259</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="75">
@@ -4377,19 +4377,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="F75" t="n">
         <v>0.424</v>
       </c>
       <c r="G75" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="H75" t="n">
         <v>0.001</v>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>0.0049</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="76">
@@ -4430,19 +4430,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="F76" t="n">
         <v>0.424</v>
       </c>
       <c r="G76" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="H76" t="n">
         <v>0.001</v>
@@ -4468,7 +4468,7 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>0.0049</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="77">
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D77" t="n">
         <v>0.001</v>
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>0.0005</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="78">
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D78" t="n">
         <v>0.001</v>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>0.0032</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="79">
@@ -4589,19 +4589,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D79" t="n">
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="F79" t="n">
         <v>0.424</v>
       </c>
       <c r="G79" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="H79" t="n">
         <v>0.001</v>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>0.0022</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="80">
@@ -4642,19 +4642,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="F80" t="n">
         <v>0.424</v>
       </c>
       <c r="G80" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="H80" t="n">
         <v>0.001</v>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>0.0022</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="81">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D81" t="n">
         <v>0.001</v>
@@ -4707,7 +4707,7 @@
         <v>0.424</v>
       </c>
       <c r="G81" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="H81" t="n">
         <v>0.006</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>0.0025</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="82">
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D82" t="n">
         <v>0.001</v>
@@ -4760,7 +4760,7 @@
         <v>0.424</v>
       </c>
       <c r="G82" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="H82" t="n">
         <v>0.006</v>
@@ -4801,19 +4801,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D83" t="n">
         <v>0.001</v>
       </c>
       <c r="E83" t="n">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="F83" t="n">
         <v>0.211</v>
       </c>
       <c r="G83" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="H83" t="n">
         <v>0.148</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="84">
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D84" t="n">
         <v>0.001</v>
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>0.0032</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="85">
@@ -4907,19 +4907,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D85" t="n">
         <v>0.001</v>
       </c>
       <c r="E85" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="F85" t="n">
         <v>0.424</v>
       </c>
       <c r="G85" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="H85" t="n">
         <v>0.002</v>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>0.0409</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="86">
@@ -4960,19 +4960,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D86" t="n">
         <v>0.001</v>
       </c>
       <c r="E86" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="F86" t="n">
         <v>0.424</v>
       </c>
       <c r="G86" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="H86" t="n">
         <v>0.002</v>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>0.0409</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="87">
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D87" t="n">
         <v>0.001</v>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="88">
@@ -5066,7 +5066,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D88" t="n">
         <v>0.001</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>0.0032</v>
+        <v>0.0012</v>
       </c>
     </row>
   </sheetData>
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.497</v>
+        <v>22.632</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41.405</v>
+        <v>42.632</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -5206,10 +5206,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.934</v>
+        <v>5.76</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1149</v>
+        <v>0.1239</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -5252,10 +5252,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11.765</v>
+        <v>13.259</v>
       </c>
       <c r="D6" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0041</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.674</v>
+        <v>1.399</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6428</v>
+        <v>0.7058</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.519</v>
+        <v>2.43</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4719</v>
+        <v>0.4882</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.924</v>
+        <v>0.755</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8196</v>
+        <v>0.8603</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -5344,10 +5344,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.096</v>
+        <v>1.564</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7781</v>
+        <v>0.6677</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.832</v>
+        <v>1.837</v>
       </c>
       <c r="D11" t="n">
-        <v>0.608</v>
+        <v>0.6069</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.5</v>
+        <v>5.519</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1386</v>
+        <v>0.1375</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11.317</v>
+        <v>11.377</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0101</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10.26</v>
+        <v>11.424</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0165</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -5459,10 +5459,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.842</v>
+        <v>3.8</v>
       </c>
       <c r="D15" t="n">
-        <v>0.279</v>
+        <v>0.2839</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10.779</v>
+        <v>10.814</v>
       </c>
       <c r="D16" t="n">
-        <v>0.013</v>
+        <v>0.0128</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4.297</v>
+        <v>6.217</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2311</v>
+        <v>0.1015</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -5528,10 +5528,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.418</v>
+        <v>1.122</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5182</v>
+        <v>0.2894</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.714</v>
+        <v>0.633</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8699</v>
+        <v>0.889</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.637</v>
+        <v>18.867</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.0003</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.164</v>
+        <v>0.112</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9832</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -5643,10 +5643,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.7</v>
+        <v>1.519</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6368</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -5666,10 +5666,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.62</v>
+        <v>1.361</v>
       </c>
       <c r="D24" t="n">
-        <v>0.655</v>
+        <v>0.7147</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
